--- a/output/upload/S00026_2250_하나로H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2250_하나로H종신보험_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1390,11 +1410,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1476,11 +1516,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1562,11 +1622,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1648,11 +1728,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1734,11 +1834,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1820,32 +1940,88 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n"/>
+      <c r="O13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n"/>
-      <c r="Y13" s="6" t="n"/>
-      <c r="Z13" s="6" t="n"/>
-      <c r="AA13" s="6" t="n"/>
+      <c r="X13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z13" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA13" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
       <c r="AD13" s="6" t="n"/>
@@ -1870,32 +2046,88 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
-      <c r="Q14" s="6" t="n"/>
+      <c r="O14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n"/>
-      <c r="Y14" s="6" t="n"/>
-      <c r="Z14" s="6" t="n"/>
-      <c r="AA14" s="6" t="n"/>
+      <c r="X14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA14" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
       <c r="AD14" s="6" t="n"/>
@@ -1920,32 +2152,88 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
+      <c r="J15" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="6" t="n"/>
+      <c r="O15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
-      <c r="X15" s="6" t="n"/>
-      <c r="Y15" s="6" t="n"/>
-      <c r="Z15" s="6" t="n"/>
-      <c r="AA15" s="6" t="n"/>
+      <c r="X15" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y15" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z15" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA15" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
       <c r="AD15" s="6" t="n"/>
@@ -1970,32 +2258,88 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
+      <c r="J16" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="6" t="n"/>
+      <c r="O16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
-      <c r="X16" s="6" t="n"/>
-      <c r="Y16" s="6" t="n"/>
-      <c r="Z16" s="6" t="n"/>
-      <c r="AA16" s="6" t="n"/>
+      <c r="X16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z16" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA16" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
       <c r="AD16" s="6" t="n"/>
@@ -2020,32 +2364,88 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
+      <c r="J17" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
-      <c r="Q17" s="6" t="n"/>
+      <c r="O17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n"/>
-      <c r="Y17" s="6" t="n"/>
-      <c r="Z17" s="6" t="n"/>
-      <c r="AA17" s="6" t="n"/>
+      <c r="X17" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y17" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z17" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA17" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB17" s="6" t="n"/>
       <c r="AC17" s="6" t="n"/>
       <c r="AD17" s="6" t="n"/>
@@ -2070,32 +2470,88 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2250A01</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
+      <c r="J18" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="6" t="n"/>
+      <c r="O18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
-      <c r="X18" s="6" t="n"/>
-      <c r="Y18" s="6" t="n"/>
-      <c r="Z18" s="6" t="n"/>
-      <c r="AA18" s="6" t="n"/>
+      <c r="X18" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y18" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z18" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA18" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB18" s="6" t="n"/>
       <c r="AC18" s="6" t="n"/>
       <c r="AD18" s="6" t="n"/>

--- a/output/upload/S00026_2250_하나로H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2250_하나로H종신보험_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>2250001</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">

--- a/output/upload/S00026_2250_하나로H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2250_하나로H종신보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV22"/>
+  <dimension ref="A1:AV78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2576,32 +2576,88 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2250A02</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>2250002</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
+      <c r="J19" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="n"/>
       <c r="N19" s="6" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="6" t="n"/>
+      <c r="O19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R19" s="6" t="n"/>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
-      <c r="X19" s="6" t="n"/>
-      <c r="Y19" s="6" t="n"/>
-      <c r="Z19" s="6" t="n"/>
-      <c r="AA19" s="6" t="n"/>
+      <c r="X19" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y19" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z19" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA19" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB19" s="6" t="n"/>
       <c r="AC19" s="6" t="n"/>
       <c r="AD19" s="6" t="n"/>
@@ -2626,32 +2682,88 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2250A02</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>2250002</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
+      <c r="J20" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n"/>
-      <c r="Q20" s="6" t="n"/>
+      <c r="O20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R20" s="6" t="n"/>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
-      <c r="X20" s="6" t="n"/>
-      <c r="Y20" s="6" t="n"/>
-      <c r="Z20" s="6" t="n"/>
-      <c r="AA20" s="6" t="n"/>
+      <c r="X20" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y20" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z20" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA20" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB20" s="6" t="n"/>
       <c r="AC20" s="6" t="n"/>
       <c r="AD20" s="6" t="n"/>
@@ -2676,32 +2788,88 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2250A02</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>2250002</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
+      <c r="J21" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
+      <c r="O21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
-      <c r="X21" s="6" t="n"/>
-      <c r="Y21" s="6" t="n"/>
-      <c r="Z21" s="6" t="n"/>
-      <c r="AA21" s="6" t="n"/>
+      <c r="X21" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z21" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA21" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB21" s="6" t="n"/>
       <c r="AC21" s="6" t="n"/>
       <c r="AD21" s="6" t="n"/>
@@ -2726,32 +2894,88 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2250A02</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>2250002</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
+      <c r="J22" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
+      <c r="O22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R22" s="6" t="n"/>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
-      <c r="AA22" s="6" t="n"/>
+      <c r="X22" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y22" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z22" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA22" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB22" s="6" t="n"/>
       <c r="AC22" s="6" t="n"/>
       <c r="AD22" s="6" t="n"/>
@@ -2774,6 +2998,4206 @@
       <c r="AU22" s="6" t="n"/>
       <c r="AV22" s="6" t="n"/>
     </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2250A02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2250002</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>15</v>
+      </c>
+      <c r="K23" t="n">
+        <v>60</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>999</v>
+      </c>
+      <c r="P23" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2250A02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2250002</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>15</v>
+      </c>
+      <c r="K24" t="n">
+        <v>60</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>999</v>
+      </c>
+      <c r="P24" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2250A02</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2250002</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>20</v>
+      </c>
+      <c r="K25" t="n">
+        <v>60</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>999</v>
+      </c>
+      <c r="P25" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2250A02</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2250002</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>20</v>
+      </c>
+      <c r="K26" t="n">
+        <v>60</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>999</v>
+      </c>
+      <c r="P26" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2250A02</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2250002</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>20</v>
+      </c>
+      <c r="K27" t="n">
+        <v>60</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>999</v>
+      </c>
+      <c r="P27" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2250A02</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2250002</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>20</v>
+      </c>
+      <c r="K28" t="n">
+        <v>60</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>999</v>
+      </c>
+      <c r="P28" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2250A02</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2250002</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>20</v>
+      </c>
+      <c r="K29" t="n">
+        <v>60</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>999</v>
+      </c>
+      <c r="P29" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2250A02</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2250002</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>20</v>
+      </c>
+      <c r="K30" t="n">
+        <v>60</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>999</v>
+      </c>
+      <c r="P30" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2250A03</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2250003</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>15</v>
+      </c>
+      <c r="K31" t="n">
+        <v>60</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>999</v>
+      </c>
+      <c r="P31" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2250A03</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2250003</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>15</v>
+      </c>
+      <c r="K32" t="n">
+        <v>60</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>999</v>
+      </c>
+      <c r="P32" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2250A03</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2250003</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>15</v>
+      </c>
+      <c r="K33" t="n">
+        <v>60</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>999</v>
+      </c>
+      <c r="P33" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2250A03</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2250003</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>15</v>
+      </c>
+      <c r="K34" t="n">
+        <v>60</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>999</v>
+      </c>
+      <c r="P34" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2250A03</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2250003</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>15</v>
+      </c>
+      <c r="K35" t="n">
+        <v>60</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>999</v>
+      </c>
+      <c r="P35" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2250A03</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2250003</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>15</v>
+      </c>
+      <c r="K36" t="n">
+        <v>60</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>999</v>
+      </c>
+      <c r="P36" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2250A03</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2250003</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>20</v>
+      </c>
+      <c r="K37" t="n">
+        <v>60</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>999</v>
+      </c>
+      <c r="P37" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2250A03</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2250003</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>20</v>
+      </c>
+      <c r="K38" t="n">
+        <v>60</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>999</v>
+      </c>
+      <c r="P38" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2250A03</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2250003</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>20</v>
+      </c>
+      <c r="K39" t="n">
+        <v>60</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>999</v>
+      </c>
+      <c r="P39" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2250A03</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2250003</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>20</v>
+      </c>
+      <c r="K40" t="n">
+        <v>60</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>999</v>
+      </c>
+      <c r="P40" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2250A03</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2250003</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>20</v>
+      </c>
+      <c r="K41" t="n">
+        <v>60</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>999</v>
+      </c>
+      <c r="P41" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2250A03</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2250003</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>20</v>
+      </c>
+      <c r="K42" t="n">
+        <v>60</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>999</v>
+      </c>
+      <c r="P42" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2250A04</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2250004</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>15</v>
+      </c>
+      <c r="K43" t="n">
+        <v>60</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>999</v>
+      </c>
+      <c r="P43" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2250A04</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2250004</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>15</v>
+      </c>
+      <c r="K44" t="n">
+        <v>60</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>999</v>
+      </c>
+      <c r="P44" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2250A04</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2250004</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>15</v>
+      </c>
+      <c r="K45" t="n">
+        <v>60</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>999</v>
+      </c>
+      <c r="P45" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2250A04</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2250004</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>15</v>
+      </c>
+      <c r="K46" t="n">
+        <v>60</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>999</v>
+      </c>
+      <c r="P46" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2250A04</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2250004</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>15</v>
+      </c>
+      <c r="K47" t="n">
+        <v>60</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>999</v>
+      </c>
+      <c r="P47" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2250A04</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2250004</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>15</v>
+      </c>
+      <c r="K48" t="n">
+        <v>60</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>999</v>
+      </c>
+      <c r="P48" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2250A04</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2250004</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>20</v>
+      </c>
+      <c r="K49" t="n">
+        <v>60</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>999</v>
+      </c>
+      <c r="P49" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2250A04</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2250004</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>20</v>
+      </c>
+      <c r="K50" t="n">
+        <v>60</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>999</v>
+      </c>
+      <c r="P50" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2250A04</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2250004</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>20</v>
+      </c>
+      <c r="K51" t="n">
+        <v>60</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>999</v>
+      </c>
+      <c r="P51" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X51" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2250A04</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2250004</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>20</v>
+      </c>
+      <c r="K52" t="n">
+        <v>60</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>999</v>
+      </c>
+      <c r="P52" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2250A04</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2250004</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>20</v>
+      </c>
+      <c r="K53" t="n">
+        <v>60</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>999</v>
+      </c>
+      <c r="P53" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X53" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2250A04</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2250004</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>20</v>
+      </c>
+      <c r="K54" t="n">
+        <v>60</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>999</v>
+      </c>
+      <c r="P54" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2250A05</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2250005</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>15</v>
+      </c>
+      <c r="K55" t="n">
+        <v>60</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>999</v>
+      </c>
+      <c r="P55" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2250A05</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2250005</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>15</v>
+      </c>
+      <c r="K56" t="n">
+        <v>60</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>999</v>
+      </c>
+      <c r="P56" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2250A05</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2250005</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>15</v>
+      </c>
+      <c r="K57" t="n">
+        <v>60</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>999</v>
+      </c>
+      <c r="P57" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2250A05</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2250005</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>15</v>
+      </c>
+      <c r="K58" t="n">
+        <v>60</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>999</v>
+      </c>
+      <c r="P58" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X58" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2250A05</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2250005</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>15</v>
+      </c>
+      <c r="K59" t="n">
+        <v>60</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>999</v>
+      </c>
+      <c r="P59" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X59" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2250A05</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2250005</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>15</v>
+      </c>
+      <c r="K60" t="n">
+        <v>60</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>999</v>
+      </c>
+      <c r="P60" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X60" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2250A05</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2250005</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>20</v>
+      </c>
+      <c r="K61" t="n">
+        <v>60</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>999</v>
+      </c>
+      <c r="P61" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2250A05</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2250005</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>20</v>
+      </c>
+      <c r="K62" t="n">
+        <v>60</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>999</v>
+      </c>
+      <c r="P62" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2250A05</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2250005</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>20</v>
+      </c>
+      <c r="K63" t="n">
+        <v>60</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>999</v>
+      </c>
+      <c r="P63" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X63" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2250A05</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2250005</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>20</v>
+      </c>
+      <c r="K64" t="n">
+        <v>60</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>999</v>
+      </c>
+      <c r="P64" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X64" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2250A05</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2250005</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>20</v>
+      </c>
+      <c r="K65" t="n">
+        <v>60</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>999</v>
+      </c>
+      <c r="P65" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X65" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2250A05</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2250005</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 표준체</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>20</v>
+      </c>
+      <c r="K66" t="n">
+        <v>60</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>999</v>
+      </c>
+      <c r="P66" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X66" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2250A06</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2250006</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>15</v>
+      </c>
+      <c r="K67" t="n">
+        <v>60</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>999</v>
+      </c>
+      <c r="P67" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2250A06</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2250006</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>15</v>
+      </c>
+      <c r="K68" t="n">
+        <v>60</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>999</v>
+      </c>
+      <c r="P68" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2250A06</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2250006</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>15</v>
+      </c>
+      <c r="K69" t="n">
+        <v>60</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>999</v>
+      </c>
+      <c r="P69" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X69" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2250A06</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2250006</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>15</v>
+      </c>
+      <c r="K70" t="n">
+        <v>60</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>999</v>
+      </c>
+      <c r="P70" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X70" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2250A06</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2250006</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>15</v>
+      </c>
+      <c r="K71" t="n">
+        <v>60</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>999</v>
+      </c>
+      <c r="P71" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X71" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2250A06</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2250006</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>15</v>
+      </c>
+      <c r="K72" t="n">
+        <v>60</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>999</v>
+      </c>
+      <c r="P72" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X72" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2250A06</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2250006</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>20</v>
+      </c>
+      <c r="K73" t="n">
+        <v>60</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>999</v>
+      </c>
+      <c r="P73" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2250A06</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2250006</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>20</v>
+      </c>
+      <c r="K74" t="n">
+        <v>60</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>999</v>
+      </c>
+      <c r="P74" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2250A06</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2250006</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>20</v>
+      </c>
+      <c r="K75" t="n">
+        <v>60</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>999</v>
+      </c>
+      <c r="P75" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X75" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2250A06</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2250006</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>20</v>
+      </c>
+      <c r="K76" t="n">
+        <v>60</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>999</v>
+      </c>
+      <c r="P76" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X76" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2250A06</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2250006</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>20</v>
+      </c>
+      <c r="K77" t="n">
+        <v>60</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>999</v>
+      </c>
+      <c r="P77" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X77" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2250A06</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2250006</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>한화생명 하나로H종신보험 무배당 보장형 계약 3종(해약환급금 일부지급형Ⅲ) 건강체</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>20</v>
+      </c>
+      <c r="K78" t="n">
+        <v>60</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>999</v>
+      </c>
+      <c r="P78" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X78" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="L3:AV3"/>
